--- a/Result/checksun_type/水泥熟料.xlsx
+++ b/Result/checksun_type/水泥熟料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>25.82</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>25.42</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25.42</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1436224.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1424472.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1424472.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2096104.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2996235.98</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2996235.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-217468.8723230569</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1436224</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1436224.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>25.7</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>25.36</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>25.36</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>439725.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1385394.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1385394.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2453313.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2992311.72</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2992311.72</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-208762.9886508698</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>439725</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>439725.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>25.64</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>25.31</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>25.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1501799.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2136472.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2136472.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>3128002.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>3005349.36</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>3005349.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-82102.44095307123</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1501799</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1501799.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>25.75</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>25.34</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>2047963.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2423759.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2423759</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>3007961.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>2993427.38</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>2993427.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-12020.21420789231</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>2047963</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2047963.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>25.89</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>25.21</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>25.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1696650.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2674372.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2674372.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2900423.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>2969257.8</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>2969257.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>30008.97450693091</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1696650</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1696650.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>25.97</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>25.3</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>25.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1240836.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2767736.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2767736.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>2870007.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2951610.74</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2951610.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>126619.6021528593</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1240836</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1240836.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>26.11</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>25.29</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>25.11</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>4195114.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>3521232.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>3521232.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2815478.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2934653.98</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2934653.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>308949.8701415835</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>4195114</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>4195114.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>26.21</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>25.06</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>2938232.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>4119532.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>4119532</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2513925.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2871310.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2871310.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>241857.971906133</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>2938232</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2938232.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>25.93</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>25.01</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>25.01</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>3301032.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3592164.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3592164.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2382852.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>2887365.38</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>2887365.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>272040.5468588425</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>3301032</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3301032.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>25.64</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>24.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2163467.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3126473.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>3126473.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2282476.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>2847130.04</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>2847130.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>266571.3486891831</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2163467</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2163467.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>24.88</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>24.88</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5008319.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2972279.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2972279.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2167880.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>2819112.62</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>2819112.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>371119.7674221992</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5008319</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5008319.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>15.5</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>15.61</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1529519.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1211570.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1211570.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1455383.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1488562.2</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1488562.2</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>7424.0549043559</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1529519</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1529519.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>15.44</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>15.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>552889.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1531761.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1531761.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1383918.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1525316.78</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1525316.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-11250.54924079753</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>552889</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>552889.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>15.45</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>15.52</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1602674.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1702430.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1702430.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1381594.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1543293.42</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1543293.42</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>67112.17873901175</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1602674</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1602674.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>15.48</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>15.62</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15.62</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1670308.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1614423.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1614423.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1303882.4</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1523738.54</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1523738.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>64185.10518377437</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1670308</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1670308.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>15.54</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>15.54</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>15.63</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>15.63</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>702461.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1603478.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1603478.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1184677.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1500194.58</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1500194.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>50464.74634830048</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>702461</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>702461.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>15.58</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>15.64</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>15.64</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>3130474.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1699196.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1699196.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1213694.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1492008.92</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1492008.92</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>132759.8142137555</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>3130474</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>3130474.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>15.61</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>15.66</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1406236.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1236075.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1236075.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1008882.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1439500.94</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1439500.94</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-14561.47505751392</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1406236</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1406236.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>15.59</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>15.66</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1162637.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1060757.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1060757.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>930042.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1427734.98</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1427734.98</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-39760.62133584497</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1162637</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1162637.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>15.55</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1615584.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>993341.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>993341.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>948198.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1422825.74</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1422825.74</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-48239.48668575194</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1615584</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1615584.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>15.49</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1181050.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>765877.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>765877.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1338803.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1439931.86</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1439931.86</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-107159.3483754136</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1181050</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1181050.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>15.47</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.67</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.67</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>814870.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>728193.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>728193.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1376350.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1469097.32</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1469097.32</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-140946.2454900942</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>814870</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>814870.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>15.01</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2296179.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>1772771.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>1772771.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>2871804.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2127351.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2127351.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-113079.6313257013</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2296179</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2296179.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>15.01</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>2724161.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>1588940.0</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>1588940</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>2969573.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2187633.46</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2187633.46</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-124878.8330158251</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>2724161</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>2724161.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,21 +11377,17 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AM26" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AO26" t="inlineStr">
         <is>
           <t>15.01</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>15.01</t>
-        </is>
-      </c>
       <c r="AP26" t="inlineStr">
         <is>
           <t>32.29</t>
@@ -11576,20 +11428,16 @@
           <t>1090295.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1616637.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1616637.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>2881734.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2369216.76</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2369216.76</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-183130.0913940081</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1090295</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1090295.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>15.02</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>1497444.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>2212682.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>2212682.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3107504.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2380023.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2380023.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-84748.74295591237</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>1497444</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1497444.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15.03</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1255777.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>3689238.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>3689238.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3145706.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2414310.08</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2414310.08</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>15199.67420407897</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1255777</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1255777.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>14.99</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>15.04</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1377023.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>3970837.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>3970837.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3186018.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2461469.72</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2461469.72</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>183333.1746396348</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1377023</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1377023.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,21 +13097,17 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AM30" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="AO30" t="inlineStr">
         <is>
           <t>14.97</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>15.05</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
       <c r="AP30" t="inlineStr">
         <is>
           <t>48.84</t>
@@ -13320,20 +13148,16 @@
           <t>2862648.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4350207.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4350207</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3555590.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2528642.34</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2528642.34</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>403985.6333104419</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2862648</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2862648.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,21 +13527,17 @@
           <t>15.0</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AM31" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="AO31" t="inlineStr">
         <is>
           <t>14.97</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
       <c r="AP31" t="inlineStr">
         <is>
           <t>61.87</t>
@@ -13756,20 +13578,16 @@
           <t>4070520.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>4146831.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>4146831</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3375587.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2521002.36</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2521002.36</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>545601.2659362219</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>4070520</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>4070520.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>14.98</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>8880223.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>4002326.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>4002326.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3146122.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2462772.2</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2462772.2</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>599008.6959039001</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>8880223</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>8880223.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,21 +14387,17 @@
           <t>14.96</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AM33" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AO33" t="inlineStr">
         <is>
           <t>14.96</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
       <c r="AP33" t="inlineStr">
         <is>
           <t>24.37</t>
@@ -14628,20 +14438,16 @@
           <t>2663774.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2602175.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2602175.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2428155.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2387559.66</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2387559.66</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>138586.5352897295</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>2663774</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>2663774.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,21 +14817,17 @@
           <t>14.95</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AM34" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AO34" t="inlineStr">
         <is>
           <t>14.96</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
       <c r="AP34" t="inlineStr">
         <is>
           <t>10.98</t>
@@ -15064,20 +14868,16 @@
           <t>3273870.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2401200.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2401200.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2370937.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2438206.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2438206.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>141939.1795805674</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3273870</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3273870.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>37.84</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>36.94</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>120416322.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>280072163.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>280072163</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>277426832.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>200154771.9</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>200154771.9</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>14388099.54638198</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>120416322</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>120416322.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>37.76000000000001</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>36.85</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>36.89</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>36.89</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>206096332.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>311473909.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>311473909.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>275431895.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>202581225.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>202581225</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>31383448.08971417</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>206096332</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>206096332.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>37.62</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>36.86</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>651269647.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>352300593.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>352300593.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>266468929.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>202369157.08</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>202369157.08</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>45361678.93412757</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>651269647</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>651269647.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>37.48</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>36.72</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>36.82</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>36.82</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>218965347.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>285520921.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>285520921.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>227340167.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>193138591.86</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>193138591.86</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>16013379.28564209</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>218965347</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>218965347.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>37.48</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>36.73</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>36.73</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>36.8</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>203613167.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>281712122.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>281712122.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>217589197.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>191062131.4</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>191062131.4</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>19833648.38474703</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>203613167</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>203613167.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>37.4</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>36.72</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>277425056.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>274781502.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>274781502.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>209108494.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>189889393.8</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>189889393.8</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>26227707.51258457</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>277425056</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>277425056.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>37.27</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>36.69</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>36.75</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>36.75</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>410229751.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>239389881.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>239389881.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>193854808.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>186839318.84</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>186839318.84</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>26516957.17690307</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>410229751</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>410229751.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>37.21999999999999</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>36.74</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>36.74</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>317371288.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>180637265.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>180637265</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>167115803.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>181158923.66</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>181158923.66</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>11754062.33389726</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>317371288</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>317371288.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>37.14</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>36.71</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>199921349.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>169159413.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>169159413.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>165563914.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>177543829.44</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>177543829.44</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>193545.6533926129</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>199921349</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>199921349.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>36.88</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>36.58</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>36.69</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>36.69</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>168960070.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>153466272.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>153466272.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>157164946.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>177846992.98</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>177846992.98</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-3744468.484949499</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>168960070</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>168960070.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>36.63</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>36.56</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>36.69</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>36.69</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>100466950.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>143435486.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>143435486.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>163956437.7</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>180812768.7</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>180812768.7</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-5919192.058118582</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>100466950</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>100466950.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>21.12</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>22.5</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>671687205.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>626195530.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>626195530.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>622132821.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>733146356.66</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>733146356.66</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>21189677.43851745</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>671687205</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>671687205.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>20.81</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>22.5</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>494560639.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>640193393.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>640193393.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>603452151.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>734438326.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>734438326</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>18607123.49500573</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>494560639</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>494560639.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>20.74</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>21.57</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>22.54</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>22.54</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>952963874.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>684968154.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>684968154</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>608460649.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>745292054.98</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>745292054.98</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>33231066.95088148</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>952963874</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>952963874.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>20.8</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>22.56</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>508895219.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>572334943.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>572334943.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>541620112.7</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>742408659.92</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>742408659.92</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>3820958.603886724</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>508895219</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>508895219.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>20.99</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>21.78</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>22.6</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>502870717.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>585463875.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>585463875.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>527086711.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>747869455.14</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>747869455.14</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>9248839.765184045</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>502870717</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>502870717.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>21.23</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>22.64</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>22.64</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>741676517.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>618070111.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>618070111.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>508904183.5</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>743559492.34</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>743559492.34</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>17318122.36113799</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>741676517</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>741676517.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>21.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>22.02</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>22.68</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>22.68</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>718434443.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>566710909.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>566710909.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>472748946.4</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>736966797.76</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>736966797.76</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>2640828.842460155</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>718434443</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>718434443.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>21.83</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>22.71</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>22.71</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>389797823.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>531953145.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>531953145.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>473420250.2</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>729928690.36</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>729928690.36</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-15930826.42859614</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>389797823</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>389797823.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>21.91</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>22.24</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>22.72</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>22.72</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>574539878.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>510905281.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>510905281.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>532030878.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>733920278.26</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>733920278.26</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-6681738.014798105</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>574539878</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>574539878.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>21.96</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>22.31</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>22.74</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>22.74</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>665901898.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>468709547.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>468709547.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>524403302.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>731032785.28</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>731032785.28</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-13023912.6731295</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>665901898</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>665901898.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>21.88</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>22.75</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>484880504.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>399738255.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>399738255.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>517022636.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>736449789.18</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>736449789.1799999</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-31407810.30384827</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>484880504</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>484880504.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
